--- a/e2e-screenshots/sales-history-voided-inclusion/fixtures/SOLDTODAY_SALES.xlsx
+++ b/e2e-screenshots/sales-history-voided-inclusion/fixtures/SOLDTODAY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-STT-ACTIVE</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-STT-VOIDED</v>
@@ -562,7 +562,7 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>2026-07-27</v>
+        <v>2026-08-02</v>
       </c>
       <c r="Q3" t="str">
         <v>Refund</v>

--- a/e2e-screenshots/sales-history-voided-inclusion/fixtures/SOLDTODAY_SALES.xlsx
+++ b/e2e-screenshots/sales-history-voided-inclusion/fixtures/SOLDTODAY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-STT-ACTIVE</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-STT-VOIDED</v>
@@ -562,7 +562,7 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-08</v>
       </c>
       <c r="Q3" t="str">
         <v>Refund</v>

--- a/e2e-screenshots/sales-history-voided-inclusion/fixtures/SOLDTODAY_SALES.xlsx
+++ b/e2e-screenshots/sales-history-voided-inclusion/fixtures/SOLDTODAY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-STT-ACTIVE</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-STT-VOIDED</v>
@@ -562,7 +562,7 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>2026-08-08</v>
+        <v>2026-08-11</v>
       </c>
       <c r="Q3" t="str">
         <v>Refund</v>

--- a/e2e-screenshots/sales-history-voided-inclusion/fixtures/SOLDTODAY_SALES.xlsx
+++ b/e2e-screenshots/sales-history-voided-inclusion/fixtures/SOLDTODAY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-STT-ACTIVE</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-STT-VOIDED</v>
@@ -562,7 +562,7 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>2026-08-11</v>
+        <v>2026-09-05</v>
       </c>
       <c r="Q3" t="str">
         <v>Refund</v>

--- a/e2e-screenshots/sales-history-voided-inclusion/fixtures/SOLDTODAY_SALES.xlsx
+++ b/e2e-screenshots/sales-history-voided-inclusion/fixtures/SOLDTODAY_SALES.xlsx
@@ -461,7 +461,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="B2" t="str">
         <v>AMZ-STT-ACTIVE</v>
@@ -517,7 +517,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="B3" t="str">
         <v>AMZ-STT-VOIDED</v>
@@ -562,7 +562,7 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>2026-09-05</v>
+        <v>2026-09-09</v>
       </c>
       <c r="Q3" t="str">
         <v>Refund</v>
